--- a/昌邑门店清单.xlsx
+++ b/昌邑门店清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16640" windowHeight="14780"/>
+    <workbookView windowWidth="15900" windowHeight="15140"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1145,7 +1145,7 @@
     <t>二级甲等医院(第一终端-等级医院)</t>
   </si>
   <si>
-    <t>119.392567,36.852959</t>
+    <t>119.413008,36.853182</t>
   </si>
   <si>
     <t>昌邑昌城医院</t>
@@ -4216,7 +4216,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J269"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
@@ -4263,14 +4263,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" hidden="1" spans="1:10">
       <c r="A2" s="1">
         <v>325036</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
@@ -4293,14 +4292,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" hidden="1" spans="1:10">
       <c r="A3" s="1">
         <v>308028</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
         <v>19</v>
       </c>
@@ -4323,18 +4321,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" hidden="1" spans="1:10">
       <c r="A4" s="1">
         <v>302852</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
         <v>24</v>
       </c>
@@ -4351,7 +4347,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:10">
+    <row r="5" s="1" customFormat="1" hidden="1" spans="1:10">
       <c r="A5" s="1">
         <v>317474</v>
       </c>
@@ -4380,14 +4376,13 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" hidden="1" spans="1:10">
       <c r="A6" s="1">
         <v>304032</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
         <v>31</v>
       </c>
@@ -4410,14 +4405,13 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" hidden="1" spans="1:10">
       <c r="A7" s="1">
         <v>309756</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
         <v>35</v>
       </c>
@@ -4440,14 +4434,13 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" hidden="1" spans="1:10">
       <c r="A8" s="1">
         <v>316740</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
         <v>39</v>
       </c>
@@ -4470,7 +4463,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:10">
+    <row r="9" s="1" customFormat="1" hidden="1" spans="1:10">
       <c r="A9" s="1">
         <v>303956</v>
       </c>
@@ -4499,7 +4492,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="1:10">
+    <row r="10" s="1" customFormat="1" hidden="1" spans="1:10">
       <c r="A10" s="1">
         <v>149383</v>
       </c>
@@ -4528,14 +4521,13 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" hidden="1" spans="1:10">
       <c r="A11" s="1">
         <v>334283</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
         <v>53</v>
       </c>
@@ -4558,14 +4550,13 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" hidden="1" spans="1:10">
       <c r="A12" s="1">
         <v>312076</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
         <v>57</v>
       </c>
@@ -4588,14 +4579,13 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" hidden="1" spans="1:10">
       <c r="A13" s="1">
         <v>304369</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
         <v>61</v>
       </c>
@@ -4618,7 +4608,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:10">
+    <row r="14" s="1" customFormat="1" hidden="1" spans="1:10">
       <c r="A14" s="1">
         <v>301555</v>
       </c>
@@ -4647,14 +4637,13 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" hidden="1" spans="1:10">
       <c r="A15" s="1">
         <v>300324</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
         <v>69</v>
       </c>
@@ -4677,14 +4666,13 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" hidden="1" spans="1:10">
       <c r="A16" s="1">
         <v>309715</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
         <v>73</v>
       </c>
@@ -4707,14 +4695,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" hidden="1" spans="1:10">
       <c r="A17" s="1">
         <v>314944</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
         <v>77</v>
       </c>
@@ -4737,7 +4724,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" spans="1:10">
+    <row r="18" s="1" customFormat="1" hidden="1" spans="1:10">
       <c r="A18" s="1">
         <v>347637</v>
       </c>
@@ -4766,7 +4753,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" spans="1:10">
+    <row r="19" s="1" customFormat="1" hidden="1" spans="1:10">
       <c r="A19" s="1">
         <v>301556</v>
       </c>
@@ -4796,18 +4783,16 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" hidden="1" spans="1:10">
       <c r="A20" s="1">
         <v>304085</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
         <v>13</v>
       </c>
@@ -4824,14 +4809,13 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" hidden="1" spans="1:10">
       <c r="A21" s="1">
         <v>324534</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
         <v>92</v>
       </c>
@@ -4854,14 +4838,13 @@
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" hidden="1" spans="1:10">
       <c r="A22" s="1">
         <v>342556</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
         <v>92</v>
       </c>
@@ -4884,7 +4867,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" spans="1:10">
+    <row r="23" s="1" customFormat="1" hidden="1" spans="1:10">
       <c r="A23" s="1">
         <v>300549</v>
       </c>
@@ -4913,7 +4896,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" spans="1:10">
+    <row r="24" s="1" customFormat="1" hidden="1" spans="1:10">
       <c r="A24" s="1">
         <v>330102</v>
       </c>
@@ -4942,14 +4925,13 @@
         <v>106</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" hidden="1" spans="1:10">
       <c r="A25" s="1">
         <v>323661</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
         <v>108</v>
       </c>
@@ -4972,14 +4954,13 @@
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" hidden="1" spans="1:10">
       <c r="A26" s="1">
         <v>315261</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
         <v>112</v>
       </c>
@@ -5002,14 +4983,13 @@
         <v>114</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" hidden="1" spans="1:10">
       <c r="A27" s="1">
         <v>314820</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
         <v>116</v>
       </c>
@@ -5032,7 +5012,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" spans="1:10">
+    <row r="28" s="1" customFormat="1" hidden="1" spans="1:10">
       <c r="A28" s="1">
         <v>347663</v>
       </c>
@@ -5061,14 +5041,13 @@
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" hidden="1" spans="1:10">
       <c r="A29" s="1">
         <v>356313</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
         <v>124</v>
       </c>
@@ -5091,18 +5070,16 @@
         <v>126</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" hidden="1" spans="1:10">
       <c r="A30" s="1">
         <v>316451</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E30" s="1"/>
       <c r="F30" s="1" t="s">
         <v>41</v>
       </c>
@@ -5119,7 +5096,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" hidden="1" spans="1:10">
       <c r="A31" s="1">
         <v>315155</v>
       </c>
@@ -5148,7 +5125,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" hidden="1" spans="1:10">
       <c r="A32" s="1">
         <v>300382</v>
       </c>
@@ -5177,7 +5154,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" hidden="1" spans="1:10">
       <c r="A33" s="1">
         <v>121326</v>
       </c>
@@ -5206,7 +5183,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" hidden="1" spans="1:10">
       <c r="A34" s="1">
         <v>300631</v>
       </c>
@@ -5235,7 +5212,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" hidden="1" spans="1:10">
       <c r="A35" s="1">
         <v>307142</v>
       </c>
@@ -5264,7 +5241,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" hidden="1" spans="1:10">
       <c r="A36" s="1">
         <v>306160</v>
       </c>
@@ -5293,7 +5270,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" hidden="1" spans="1:10">
       <c r="A37" s="1">
         <v>337766</v>
       </c>
@@ -5322,7 +5299,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" hidden="1" spans="1:10">
       <c r="A38" s="1">
         <v>172754</v>
       </c>
@@ -5354,7 +5331,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" hidden="1" spans="1:10">
       <c r="A39" s="1">
         <v>303178</v>
       </c>
@@ -5383,7 +5360,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" hidden="1" spans="1:10">
       <c r="A40" s="1">
         <v>312987</v>
       </c>
@@ -5412,7 +5389,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" hidden="1" spans="1:10">
       <c r="A41" s="1">
         <v>318606</v>
       </c>
@@ -5441,7 +5418,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" hidden="1" spans="1:10">
       <c r="A42" s="1">
         <v>315454</v>
       </c>
@@ -5470,7 +5447,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" hidden="1" spans="1:10">
       <c r="A43" s="1">
         <v>301243</v>
       </c>
@@ -5499,7 +5476,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" hidden="1" spans="1:10">
       <c r="A44" s="1">
         <v>120837</v>
       </c>
@@ -5528,7 +5505,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" hidden="1" spans="1:10">
       <c r="A45" s="1">
         <v>313224</v>
       </c>
@@ -5557,7 +5534,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" hidden="1" spans="1:10">
       <c r="A46" s="1">
         <v>300320</v>
       </c>
@@ -5586,7 +5563,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" hidden="1" spans="1:10">
       <c r="A47" s="1">
         <v>306973</v>
       </c>
@@ -5615,7 +5592,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" hidden="1" spans="1:10">
       <c r="A48" s="1">
         <v>358012</v>
       </c>
@@ -5644,7 +5621,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" hidden="1" spans="1:10">
       <c r="A49" s="1">
         <v>356203</v>
       </c>
@@ -5673,7 +5650,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" hidden="1" spans="1:10">
       <c r="A50" s="1">
         <v>347641</v>
       </c>
@@ -5702,7 +5679,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" hidden="1" spans="1:10">
       <c r="A51" s="1">
         <v>312518</v>
       </c>
@@ -5731,7 +5708,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" hidden="1" spans="1:10">
       <c r="A52" s="1">
         <v>333002</v>
       </c>
@@ -5760,7 +5737,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" hidden="1" spans="1:10">
       <c r="A53" s="1">
         <v>312093</v>
       </c>
@@ -5789,7 +5766,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" hidden="1" spans="1:10">
       <c r="A54" s="1">
         <v>313576</v>
       </c>
@@ -5818,7 +5795,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" hidden="1" spans="1:10">
       <c r="A55" s="1">
         <v>300471</v>
       </c>
@@ -5847,7 +5824,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" hidden="1" spans="1:10">
       <c r="A56" s="1">
         <v>300323</v>
       </c>
@@ -5876,7 +5853,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" hidden="1" spans="1:10">
       <c r="A57" s="1">
         <v>347639</v>
       </c>
@@ -5905,7 +5882,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" hidden="1" spans="1:10">
       <c r="A58" s="1">
         <v>300338</v>
       </c>
@@ -5934,7 +5911,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" hidden="1" spans="1:10">
       <c r="A59" s="1">
         <v>312767</v>
       </c>
@@ -5963,7 +5940,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" hidden="1" spans="1:10">
       <c r="A60" s="1">
         <v>300339</v>
       </c>
@@ -5992,7 +5969,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" hidden="1" spans="1:10">
       <c r="A61" s="1">
         <v>307413</v>
       </c>
@@ -6021,7 +5998,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" hidden="1" spans="1:10">
       <c r="A62" s="1">
         <v>307817</v>
       </c>
@@ -6050,7 +6027,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" hidden="1" spans="1:10">
       <c r="A63" s="1">
         <v>313786</v>
       </c>
@@ -6079,7 +6056,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" hidden="1" spans="1:10">
       <c r="A64" s="1">
         <v>313078</v>
       </c>
@@ -6108,7 +6085,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" hidden="1" spans="1:10">
       <c r="A65" s="1">
         <v>308467</v>
       </c>
@@ -6137,7 +6114,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" hidden="1" spans="1:10">
       <c r="A66" s="1">
         <v>301244</v>
       </c>
@@ -6166,7 +6143,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" hidden="1" spans="1:10">
       <c r="A67" s="1">
         <v>319742</v>
       </c>
@@ -6195,7 +6172,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" hidden="1" spans="1:10">
       <c r="A68" s="1">
         <v>316930</v>
       </c>
@@ -6224,7 +6201,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" hidden="1" spans="1:10">
       <c r="A69" s="1">
         <v>316448</v>
       </c>
@@ -6253,14 +6230,13 @@
         <v>285</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" hidden="1" spans="1:10">
       <c r="A70" s="1">
         <v>300433</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C70" s="1"/>
       <c r="D70" s="1" t="s">
         <v>287</v>
       </c>
@@ -6283,7 +6259,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" hidden="1" spans="1:10">
       <c r="A71" s="1">
         <v>315847</v>
       </c>
@@ -6312,7 +6288,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" hidden="1" spans="1:10">
       <c r="A72" s="1">
         <v>307271</v>
       </c>
@@ -6341,7 +6317,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" hidden="1" spans="1:10">
       <c r="A73" s="1">
         <v>310409</v>
       </c>
@@ -6370,7 +6346,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" hidden="1" spans="1:10">
       <c r="A74" s="1">
         <v>313290</v>
       </c>
@@ -6399,7 +6375,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" hidden="1" spans="1:10">
       <c r="A75" s="1">
         <v>313076</v>
       </c>
@@ -6428,7 +6404,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" hidden="1" spans="1:10">
       <c r="A76" s="1">
         <v>330373</v>
       </c>
@@ -6457,7 +6433,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" hidden="1" spans="1:10">
       <c r="A77" s="1">
         <v>320207</v>
       </c>
@@ -6486,7 +6462,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" hidden="1" spans="1:10">
       <c r="A78" s="1">
         <v>353885</v>
       </c>
@@ -6515,7 +6491,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" hidden="1" spans="1:10">
       <c r="A79" s="1">
         <v>313631</v>
       </c>
@@ -6544,7 +6520,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" hidden="1" spans="1:10">
       <c r="A80" s="1">
         <v>309291</v>
       </c>
@@ -6573,7 +6549,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" hidden="1" spans="1:10">
       <c r="A81" s="1">
         <v>301166</v>
       </c>
@@ -6602,7 +6578,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" hidden="1" spans="1:10">
       <c r="A82" s="1">
         <v>331130</v>
       </c>
@@ -6631,7 +6607,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" hidden="1" spans="1:10">
       <c r="A83" s="1">
         <v>302828</v>
       </c>
@@ -6660,7 +6636,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" hidden="1" spans="1:10">
       <c r="A84" s="1">
         <v>347437</v>
       </c>
@@ -6689,14 +6665,13 @@
         <v>344</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" hidden="1" spans="1:10">
       <c r="A85" s="1">
         <v>119589</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C85" s="1"/>
       <c r="D85" s="1" t="s">
         <v>346</v>
       </c>
@@ -6719,7 +6694,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" hidden="1" spans="1:10">
       <c r="A86" s="1">
         <v>323293</v>
       </c>
@@ -6748,7 +6723,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" hidden="1" spans="1:10">
       <c r="A87" s="1">
         <v>120930</v>
       </c>
@@ -6777,7 +6752,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" hidden="1" spans="1:10">
       <c r="A88" s="1">
         <v>324917</v>
       </c>
@@ -6806,7 +6781,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" hidden="1" spans="1:10">
       <c r="A89" s="1">
         <v>300360</v>
       </c>
@@ -6835,7 +6810,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" hidden="1" spans="1:10">
       <c r="A90" s="1">
         <v>321056</v>
       </c>
@@ -6845,7 +6820,6 @@
       <c r="D90" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E90" s="1"/>
       <c r="F90" s="1" t="s">
         <v>24</v>
       </c>
@@ -6891,7 +6865,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" hidden="1" spans="1:10">
       <c r="A92" s="1">
         <v>317642</v>
       </c>
@@ -6920,7 +6894,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" hidden="1" spans="1:10">
       <c r="A93" s="1">
         <v>300063</v>
       </c>
@@ -6949,7 +6923,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" hidden="1" spans="1:10">
       <c r="A94" s="1">
         <v>120724</v>
       </c>
@@ -6978,7 +6952,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" hidden="1" spans="1:10">
       <c r="A95" s="1">
         <v>317615</v>
       </c>
@@ -7007,7 +6981,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" hidden="1" spans="1:10">
       <c r="A96" s="1">
         <v>300019</v>
       </c>
@@ -7036,7 +7010,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" hidden="1" spans="1:10">
       <c r="A97" s="1">
         <v>314940</v>
       </c>
@@ -7065,7 +7039,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" hidden="1" spans="1:10">
       <c r="A98" s="1">
         <v>326120</v>
       </c>
@@ -7094,7 +7068,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" hidden="1" spans="1:10">
       <c r="A99" s="1">
         <v>347625</v>
       </c>
@@ -7123,7 +7097,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" hidden="1" spans="1:10">
       <c r="A100" s="1">
         <v>333440</v>
       </c>
@@ -7152,7 +7126,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" hidden="1" spans="1:10">
       <c r="A101" s="1">
         <v>300538</v>
       </c>
@@ -7181,7 +7155,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" hidden="1" spans="1:10">
       <c r="A102" s="1">
         <v>330380</v>
       </c>
@@ -7210,7 +7184,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" hidden="1" spans="1:10">
       <c r="A103" s="1">
         <v>303763</v>
       </c>
@@ -7239,7 +7213,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" hidden="1" spans="1:10">
       <c r="A104" s="1">
         <v>300641</v>
       </c>
@@ -7268,7 +7242,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" hidden="1" spans="1:10">
       <c r="A105" s="1">
         <v>330795</v>
       </c>
@@ -7297,7 +7271,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" hidden="1" spans="1:10">
       <c r="A106" s="1">
         <v>316864</v>
       </c>
@@ -7326,7 +7300,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" hidden="1" spans="1:10">
       <c r="A107" s="1">
         <v>347696</v>
       </c>
@@ -7355,7 +7329,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" hidden="1" spans="1:10">
       <c r="A108" s="1">
         <v>327415</v>
       </c>
@@ -7384,7 +7358,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" hidden="1" spans="1:10">
       <c r="A109" s="1">
         <v>318407</v>
       </c>
@@ -7413,14 +7387,13 @@
         <v>443</v>
       </c>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" hidden="1" spans="1:10">
       <c r="A110" s="1">
         <v>119583</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="C110" s="1"/>
       <c r="D110" s="1" t="s">
         <v>445</v>
       </c>
@@ -7443,7 +7416,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" hidden="1" spans="1:10">
       <c r="A111" s="1">
         <v>302197</v>
       </c>
@@ -7472,7 +7445,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" hidden="1" spans="1:10">
       <c r="A112" s="1">
         <v>354823</v>
       </c>
@@ -7501,7 +7474,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" hidden="1" spans="1:10">
       <c r="A113" s="1">
         <v>320210</v>
       </c>
@@ -7530,7 +7503,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" hidden="1" spans="1:10">
       <c r="A114" s="1">
         <v>320307</v>
       </c>
@@ -7559,7 +7532,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" hidden="1" spans="1:10">
       <c r="A115" s="1">
         <v>121346</v>
       </c>
@@ -7588,7 +7561,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" hidden="1" spans="1:10">
       <c r="A116" s="1">
         <v>317597</v>
       </c>
@@ -7617,7 +7590,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" hidden="1" spans="1:10">
       <c r="A117" s="1">
         <v>316739</v>
       </c>
@@ -7646,7 +7619,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" hidden="1" spans="1:10">
       <c r="A118" s="1">
         <v>312169</v>
       </c>
@@ -7675,7 +7648,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" hidden="1" spans="1:10">
       <c r="A119" s="1">
         <v>300327</v>
       </c>
@@ -7685,7 +7658,6 @@
       <c r="D119" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="E119" s="1"/>
       <c r="F119" s="1" t="s">
         <v>13</v>
       </c>
@@ -7702,7 +7674,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" hidden="1" spans="1:10">
       <c r="A120" s="1">
         <v>316450</v>
       </c>
@@ -7731,7 +7703,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" hidden="1" spans="1:10">
       <c r="A121" s="1">
         <v>313766</v>
       </c>
@@ -7760,7 +7732,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" hidden="1" spans="1:10">
       <c r="A122" s="1">
         <v>306533</v>
       </c>
@@ -7789,7 +7761,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" hidden="1" spans="1:10">
       <c r="A123" s="1">
         <v>121273</v>
       </c>
@@ -7799,7 +7771,6 @@
       <c r="D123" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="E123" s="1"/>
       <c r="F123" s="1" t="s">
         <v>50</v>
       </c>
@@ -7816,7 +7787,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" hidden="1" spans="1:10">
       <c r="A124" s="1">
         <v>303930</v>
       </c>
@@ -7845,7 +7816,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" hidden="1" spans="1:10">
       <c r="A125" s="1">
         <v>307589</v>
       </c>
@@ -7874,7 +7845,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" hidden="1" spans="1:10">
       <c r="A126" s="1">
         <v>300855</v>
       </c>
@@ -7903,14 +7874,13 @@
         <v>508</v>
       </c>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" hidden="1" spans="1:10">
       <c r="A127" s="1">
         <v>119459</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C127" s="1"/>
       <c r="D127" s="1" t="s">
         <v>510</v>
       </c>
@@ -7933,7 +7903,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" hidden="1" spans="1:10">
       <c r="A128" s="1">
         <v>316453</v>
       </c>
@@ -7962,7 +7932,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" hidden="1" spans="1:10">
       <c r="A129" s="1">
         <v>342174</v>
       </c>
@@ -7991,7 +7961,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" hidden="1" spans="1:10">
       <c r="A130" s="1">
         <v>300334</v>
       </c>
@@ -8020,7 +7990,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" hidden="1" spans="1:10">
       <c r="A131" s="1">
         <v>362228</v>
       </c>
@@ -8049,7 +8019,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" hidden="1" spans="1:10">
       <c r="A132" s="1">
         <v>354466</v>
       </c>
@@ -8078,7 +8048,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" hidden="1" spans="1:10">
       <c r="A133" s="1">
         <v>301281</v>
       </c>
@@ -8107,7 +8077,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" hidden="1" spans="1:10">
       <c r="A134" s="1">
         <v>331252</v>
       </c>
@@ -8136,7 +8106,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" hidden="1" spans="1:10">
       <c r="A135" s="1">
         <v>307638</v>
       </c>
@@ -8165,7 +8135,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="136" spans="1:10">
+    <row r="136" hidden="1" spans="1:10">
       <c r="A136" s="1">
         <v>303762</v>
       </c>
@@ -8194,7 +8164,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" hidden="1" spans="1:10">
       <c r="A137" s="1">
         <v>300612</v>
       </c>
@@ -8223,7 +8193,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" hidden="1" spans="1:10">
       <c r="A138" s="1">
         <v>358395</v>
       </c>
@@ -8252,7 +8222,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="139" spans="1:10">
+    <row r="139" hidden="1" spans="1:10">
       <c r="A139" s="1">
         <v>304284</v>
       </c>
@@ -8281,7 +8251,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="140" spans="1:10">
+    <row r="140" hidden="1" spans="1:10">
       <c r="A140" s="1">
         <v>331324</v>
       </c>
@@ -8310,7 +8280,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" hidden="1" spans="1:10">
       <c r="A141" s="1">
         <v>300633</v>
       </c>
@@ -8339,7 +8309,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" hidden="1" spans="1:10">
       <c r="A142" s="1">
         <v>306902</v>
       </c>
@@ -8368,7 +8338,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" hidden="1" spans="1:10">
       <c r="A143" s="1">
         <v>305446</v>
       </c>
@@ -8397,7 +8367,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" hidden="1" spans="1:10">
       <c r="A144" s="1">
         <v>332173</v>
       </c>
@@ -8426,7 +8396,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="145" spans="1:10">
+    <row r="145" hidden="1" spans="1:10">
       <c r="A145" s="1">
         <v>310103</v>
       </c>
@@ -8455,7 +8425,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" hidden="1" spans="1:10">
       <c r="A146" s="1">
         <v>332220</v>
       </c>
@@ -8484,7 +8454,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="147" spans="1:10">
+    <row r="147" hidden="1" spans="1:10">
       <c r="A147" s="1">
         <v>307412</v>
       </c>
@@ -8513,7 +8483,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="148" spans="1:10">
+    <row r="148" hidden="1" spans="1:10">
       <c r="A148" s="1">
         <v>300326</v>
       </c>
@@ -8542,7 +8512,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="149" spans="1:10">
+    <row r="149" hidden="1" spans="1:10">
       <c r="A149" s="1">
         <v>317599</v>
       </c>
@@ -8571,7 +8541,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="150" spans="1:10">
+    <row r="150" hidden="1" spans="1:10">
       <c r="A150" s="1">
         <v>315450</v>
       </c>
@@ -8600,7 +8570,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="151" spans="1:10">
+    <row r="151" hidden="1" spans="1:10">
       <c r="A151" s="1">
         <v>305416</v>
       </c>
@@ -8629,7 +8599,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="152" spans="1:10">
+    <row r="152" hidden="1" spans="1:10">
       <c r="A152" s="1">
         <v>303716</v>
       </c>
@@ -8658,7 +8628,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="153" spans="1:10">
+    <row r="153" hidden="1" spans="1:10">
       <c r="A153" s="1">
         <v>304329</v>
       </c>
@@ -8687,7 +8657,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="154" spans="1:10">
+    <row r="154" hidden="1" spans="1:10">
       <c r="A154" s="1">
         <v>300527</v>
       </c>
@@ -8716,7 +8686,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="155" spans="1:10">
+    <row r="155" hidden="1" spans="1:10">
       <c r="A155" s="1">
         <v>314839</v>
       </c>
@@ -8745,7 +8715,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="156" spans="1:10">
+    <row r="156" hidden="1" spans="1:10">
       <c r="A156" s="1">
         <v>330796</v>
       </c>
@@ -8774,7 +8744,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="157" spans="1:10">
+    <row r="157" hidden="1" spans="1:10">
       <c r="A157" s="1">
         <v>305204</v>
       </c>
@@ -8803,7 +8773,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="158" spans="1:10">
+    <row r="158" hidden="1" spans="1:10">
       <c r="A158" s="1">
         <v>308442</v>
       </c>
@@ -8832,7 +8802,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="159" spans="1:10">
+    <row r="159" hidden="1" spans="1:10">
       <c r="A159" s="1">
         <v>314017</v>
       </c>
@@ -8861,7 +8831,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="160" spans="1:10">
+    <row r="160" hidden="1" spans="1:10">
       <c r="A160" s="1">
         <v>313254</v>
       </c>
@@ -8890,7 +8860,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="161" spans="1:10">
+    <row r="161" hidden="1" spans="1:10">
       <c r="A161" s="1">
         <v>303799</v>
       </c>
@@ -8919,7 +8889,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="162" spans="1:10">
+    <row r="162" hidden="1" spans="1:10">
       <c r="A162" s="1">
         <v>313030</v>
       </c>
@@ -8948,7 +8918,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="163" spans="1:10">
+    <row r="163" hidden="1" spans="1:10">
       <c r="A163" s="1">
         <v>319559</v>
       </c>
@@ -8977,7 +8947,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="164" spans="1:10">
+    <row r="164" hidden="1" spans="1:10">
       <c r="A164" s="1">
         <v>300393</v>
       </c>
@@ -9006,7 +8976,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="165" spans="1:10">
+    <row r="165" hidden="1" spans="1:10">
       <c r="A165" s="1">
         <v>300640</v>
       </c>
@@ -9035,7 +9005,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="166" spans="1:10">
+    <row r="166" hidden="1" spans="1:10">
       <c r="A166" s="1">
         <v>363143</v>
       </c>
@@ -9064,7 +9034,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="167" spans="1:10">
+    <row r="167" hidden="1" spans="1:10">
       <c r="A167" s="1">
         <v>351186</v>
       </c>
@@ -9093,7 +9063,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="168" spans="1:10">
+    <row r="168" hidden="1" spans="1:10">
       <c r="A168" s="1">
         <v>316493</v>
       </c>
@@ -9122,14 +9092,13 @@
         <v>674</v>
       </c>
     </row>
-    <row r="169" spans="1:10">
+    <row r="169" hidden="1" spans="1:10">
       <c r="A169" s="1">
         <v>119556</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="C169" s="1"/>
       <c r="D169" s="1" t="s">
         <v>676</v>
       </c>
@@ -9152,7 +9121,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="170" spans="1:10">
+    <row r="170" hidden="1" spans="1:10">
       <c r="A170" s="1">
         <v>347631</v>
       </c>
@@ -9181,7 +9150,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="171" spans="1:10">
+    <row r="171" hidden="1" spans="1:10">
       <c r="A171" s="1">
         <v>315790</v>
       </c>
@@ -9210,7 +9179,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="172" spans="1:10">
+    <row r="172" hidden="1" spans="1:10">
       <c r="A172" s="1">
         <v>323311</v>
       </c>
@@ -9239,7 +9208,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="173" spans="1:10">
+    <row r="173" hidden="1" spans="1:10">
       <c r="A173" s="1">
         <v>302178</v>
       </c>
@@ -9268,7 +9237,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="174" spans="1:10">
+    <row r="174" hidden="1" spans="1:10">
       <c r="A174" s="1">
         <v>315444</v>
       </c>
@@ -9297,7 +9266,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="175" spans="1:10">
+    <row r="175" hidden="1" spans="1:10">
       <c r="A175" s="1">
         <v>313632</v>
       </c>
@@ -9326,7 +9295,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="176" spans="1:10">
+    <row r="176" hidden="1" spans="1:10">
       <c r="A176" s="1">
         <v>339174</v>
       </c>
@@ -9355,7 +9324,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="177" spans="1:10">
+    <row r="177" hidden="1" spans="1:10">
       <c r="A177" s="1">
         <v>347624</v>
       </c>
@@ -9384,7 +9353,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="178" spans="1:10">
+    <row r="178" hidden="1" spans="1:10">
       <c r="A178" s="1">
         <v>332614</v>
       </c>
@@ -9413,7 +9382,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="179" spans="1:10">
+    <row r="179" hidden="1" spans="1:10">
       <c r="A179" s="1">
         <v>325053</v>
       </c>
@@ -9442,7 +9411,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="180" spans="1:10">
+    <row r="180" hidden="1" spans="1:10">
       <c r="A180" s="1">
         <v>349899</v>
       </c>
@@ -9471,7 +9440,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="181" spans="1:10">
+    <row r="181" hidden="1" spans="1:10">
       <c r="A181" s="1">
         <v>357766</v>
       </c>
@@ -9500,14 +9469,13 @@
         <v>727</v>
       </c>
     </row>
-    <row r="182" spans="1:10">
+    <row r="182" hidden="1" spans="1:10">
       <c r="A182" s="1">
         <v>119561</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="C182" s="1"/>
       <c r="D182" s="1" t="s">
         <v>729</v>
       </c>
@@ -9530,7 +9498,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="183" spans="1:10">
+    <row r="183" hidden="1" spans="1:10">
       <c r="A183" s="1">
         <v>307816</v>
       </c>
@@ -9559,7 +9527,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="184" spans="1:10">
+    <row r="184" hidden="1" spans="1:10">
       <c r="A184" s="1">
         <v>353430</v>
       </c>
@@ -9569,7 +9537,6 @@
       <c r="D184" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="E184" s="1"/>
       <c r="F184" s="1" t="s">
         <v>13</v>
       </c>
@@ -9586,14 +9553,13 @@
         <v>737</v>
       </c>
     </row>
-    <row r="185" spans="1:10">
+    <row r="185" hidden="1" spans="1:10">
       <c r="A185" s="1">
         <v>119590</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="C185" s="1"/>
       <c r="D185" s="1" t="s">
         <v>739</v>
       </c>
@@ -9616,7 +9582,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="186" spans="1:10">
+    <row r="186" hidden="1" spans="1:10">
       <c r="A186" s="1">
         <v>358444</v>
       </c>
@@ -9645,7 +9611,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="187" spans="1:10">
+    <row r="187" hidden="1" spans="1:10">
       <c r="A187" s="1">
         <v>354434</v>
       </c>
@@ -9674,7 +9640,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="188" spans="1:10">
+    <row r="188" hidden="1" spans="1:10">
       <c r="A188" s="1">
         <v>354281</v>
       </c>
@@ -9703,7 +9669,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="189" spans="1:10">
+    <row r="189" hidden="1" spans="1:10">
       <c r="A189" s="1">
         <v>360570</v>
       </c>
@@ -9732,7 +9698,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="190" spans="1:10">
+    <row r="190" hidden="1" spans="1:10">
       <c r="A190" s="1">
         <v>354824</v>
       </c>
@@ -9761,7 +9727,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="191" spans="1:10">
+    <row r="191" hidden="1" spans="1:10">
       <c r="A191" s="1">
         <v>300215</v>
       </c>
@@ -9790,7 +9756,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="192" spans="1:10">
+    <row r="192" hidden="1" spans="1:10">
       <c r="A192" s="1">
         <v>353479</v>
       </c>
@@ -9800,7 +9766,6 @@
       <c r="D192" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="E192" s="1"/>
       <c r="F192" s="1" t="s">
         <v>13</v>
       </c>
@@ -9817,7 +9782,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" hidden="1" spans="1:10">
       <c r="A193" s="1">
         <v>174737</v>
       </c>
@@ -9846,7 +9811,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" hidden="1" spans="1:10">
       <c r="A194" s="1">
         <v>316338</v>
       </c>
@@ -9875,7 +9840,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="195" spans="1:10">
+    <row r="195" hidden="1" spans="1:10">
       <c r="A195" s="1">
         <v>166596</v>
       </c>
@@ -9904,7 +9869,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" hidden="1" spans="1:10">
       <c r="A196" s="1">
         <v>310429</v>
       </c>
@@ -9933,7 +9898,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" hidden="1" spans="1:10">
       <c r="A197" s="1">
         <v>300528</v>
       </c>
@@ -9962,7 +9927,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="198" spans="1:10">
+    <row r="198" hidden="1" spans="1:10">
       <c r="A198" s="1">
         <v>364308</v>
       </c>
@@ -9991,7 +9956,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="199" spans="1:10">
+    <row r="199" hidden="1" spans="1:10">
       <c r="A199" s="1">
         <v>305754</v>
       </c>
@@ -10020,7 +9985,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="200" spans="1:10">
+    <row r="200" hidden="1" spans="1:10">
       <c r="A200" s="1">
         <v>339606</v>
       </c>
@@ -10049,7 +10014,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="201" spans="1:10">
+    <row r="201" hidden="1" spans="1:10">
       <c r="A201" s="1">
         <v>303682</v>
       </c>
@@ -10078,7 +10043,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="202" spans="1:10">
+    <row r="202" hidden="1" spans="1:10">
       <c r="A202" s="1">
         <v>318577</v>
       </c>
@@ -10107,7 +10072,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="203" spans="1:10">
+    <row r="203" hidden="1" spans="1:10">
       <c r="A203" s="1">
         <v>306179</v>
       </c>
@@ -10136,7 +10101,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="204" spans="1:10">
+    <row r="204" hidden="1" spans="1:10">
       <c r="A204" s="1">
         <v>307761</v>
       </c>
@@ -10165,7 +10130,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="205" spans="1:10">
+    <row r="205" hidden="1" spans="1:10">
       <c r="A205" s="1">
         <v>308783</v>
       </c>
@@ -10194,7 +10159,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="206" spans="1:10">
+    <row r="206" hidden="1" spans="1:10">
       <c r="A206" s="1">
         <v>319988</v>
       </c>
@@ -10223,7 +10188,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="207" spans="1:10">
+    <row r="207" hidden="1" spans="1:10">
       <c r="A207" s="1">
         <v>312458</v>
       </c>
@@ -10255,7 +10220,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="208" spans="1:10">
+    <row r="208" hidden="1" spans="1:10">
       <c r="A208" s="1">
         <v>130074</v>
       </c>
@@ -10265,7 +10230,6 @@
       <c r="D208" s="1" t="s">
         <v>829</v>
       </c>
-      <c r="E208" s="1"/>
       <c r="F208" s="1" t="s">
         <v>830</v>
       </c>
@@ -10282,7 +10246,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="209" spans="1:10">
+    <row r="209" hidden="1" spans="1:10">
       <c r="A209" s="1">
         <v>135824</v>
       </c>
@@ -10311,7 +10275,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="210" spans="1:10">
+    <row r="210" hidden="1" spans="1:10">
       <c r="A210" s="1">
         <v>133074</v>
       </c>
@@ -10340,7 +10304,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="211" spans="1:10">
+    <row r="211" hidden="1" spans="1:10">
       <c r="A211" s="1">
         <v>119585</v>
       </c>
@@ -10369,14 +10333,13 @@
         <v>843</v>
       </c>
     </row>
-    <row r="212" spans="1:10">
+    <row r="212" hidden="1" spans="1:10">
       <c r="A212" s="1">
         <v>119586</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="C212" s="1"/>
       <c r="D212" s="1" t="s">
         <v>845</v>
       </c>
@@ -10399,7 +10362,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="213" spans="1:10">
+    <row r="213" hidden="1" spans="1:10">
       <c r="A213" s="1">
         <v>121115</v>
       </c>
@@ -10428,7 +10391,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="214" spans="1:10">
+    <row r="214" hidden="1" spans="1:10">
       <c r="A214" s="1">
         <v>119593</v>
       </c>
@@ -10457,7 +10420,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="215" spans="1:10">
+    <row r="215" hidden="1" spans="1:10">
       <c r="A215" s="1">
         <v>119552</v>
       </c>
@@ -10486,7 +10449,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="216" spans="1:10">
+    <row r="216" hidden="1" spans="1:10">
       <c r="A216" s="1">
         <v>121338</v>
       </c>
@@ -10515,14 +10478,13 @@
         <v>861</v>
       </c>
     </row>
-    <row r="217" spans="1:10">
+    <row r="217" hidden="1" spans="1:10">
       <c r="A217" s="1">
         <v>119594</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="C217" s="1"/>
       <c r="D217" s="1" t="s">
         <v>863</v>
       </c>
@@ -10545,14 +10507,13 @@
         <v>865</v>
       </c>
     </row>
-    <row r="218" spans="1:10">
+    <row r="218" hidden="1" spans="1:10">
       <c r="A218" s="1">
         <v>119581</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="C218" s="1"/>
       <c r="D218" s="1" t="s">
         <v>867</v>
       </c>
@@ -10575,7 +10536,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="219" spans="1:10">
+    <row r="219" hidden="1" spans="1:10">
       <c r="A219" s="1">
         <v>121342</v>
       </c>
@@ -10604,14 +10565,13 @@
         <v>872</v>
       </c>
     </row>
-    <row r="220" spans="1:10">
+    <row r="220" hidden="1" spans="1:10">
       <c r="A220" s="1">
         <v>119572</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="C220" s="1"/>
       <c r="D220" s="1" t="s">
         <v>874</v>
       </c>
@@ -10634,14 +10594,13 @@
         <v>876</v>
       </c>
     </row>
-    <row r="221" spans="1:10">
+    <row r="221" hidden="1" spans="1:10">
       <c r="A221" s="1">
         <v>119584</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="C221" s="1"/>
       <c r="D221" s="1" t="s">
         <v>878</v>
       </c>
@@ -10664,7 +10623,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="222" spans="1:10">
+    <row r="222" hidden="1" spans="1:10">
       <c r="A222" s="1">
         <v>119580</v>
       </c>
@@ -10696,7 +10655,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="223" spans="1:10">
+    <row r="223" hidden="1" spans="1:10">
       <c r="A223" s="1">
         <v>121311</v>
       </c>
@@ -10725,7 +10684,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="224" spans="1:10">
+    <row r="224" hidden="1" spans="1:10">
       <c r="A224" s="1">
         <v>121274</v>
       </c>
@@ -10754,7 +10713,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="225" spans="1:10">
+    <row r="225" hidden="1" spans="1:10">
       <c r="A225" s="1">
         <v>119596</v>
       </c>
@@ -10783,7 +10742,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="226" spans="1:10">
+    <row r="226" hidden="1" spans="1:10">
       <c r="A226" s="1">
         <v>312494</v>
       </c>
@@ -10812,7 +10771,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="227" spans="1:10">
+    <row r="227" hidden="1" spans="1:10">
       <c r="A227" s="1">
         <v>120721</v>
       </c>
@@ -10841,7 +10800,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="228" spans="1:10">
+    <row r="228" hidden="1" spans="1:10">
       <c r="A228" s="1">
         <v>121324</v>
       </c>
@@ -10873,14 +10832,13 @@
         <v>909</v>
       </c>
     </row>
-    <row r="229" spans="1:10">
+    <row r="229" hidden="1" spans="1:10">
       <c r="A229" s="1">
         <v>119546</v>
       </c>
       <c r="B229" s="1" t="s">
         <v>910</v>
       </c>
-      <c r="C229" s="1"/>
       <c r="D229" s="1" t="s">
         <v>911</v>
       </c>
@@ -10903,14 +10861,13 @@
         <v>913</v>
       </c>
     </row>
-    <row r="230" spans="1:10">
+    <row r="230" hidden="1" spans="1:10">
       <c r="A230" s="1">
         <v>119539</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>914</v>
       </c>
-      <c r="C230" s="1"/>
       <c r="D230" s="1" t="s">
         <v>915</v>
       </c>
@@ -10933,7 +10890,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="231" spans="1:10">
+    <row r="231" hidden="1" spans="1:10">
       <c r="A231" s="1">
         <v>332489</v>
       </c>
@@ -10965,7 +10922,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="232" spans="1:10">
+    <row r="232" hidden="1" spans="1:10">
       <c r="A232" s="1">
         <v>119618</v>
       </c>
@@ -10994,14 +10951,13 @@
         <v>926</v>
       </c>
     </row>
-    <row r="233" spans="1:10">
+    <row r="233" hidden="1" spans="1:10">
       <c r="A233" s="1">
         <v>119578</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>927</v>
       </c>
-      <c r="C233" s="1"/>
       <c r="D233" s="1" t="s">
         <v>928</v>
       </c>
@@ -11024,7 +10980,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="234" spans="1:10">
+    <row r="234" hidden="1" spans="1:10">
       <c r="A234" s="1">
         <v>314478</v>
       </c>
@@ -11034,7 +10990,6 @@
       <c r="D234" s="1" t="s">
         <v>932</v>
       </c>
-      <c r="E234" s="1"/>
       <c r="F234" s="1" t="s">
         <v>24</v>
       </c>
@@ -11051,7 +11006,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="235" spans="1:10">
+    <row r="235" hidden="1" spans="1:10">
       <c r="A235" s="1">
         <v>324037</v>
       </c>
@@ -11080,14 +11035,13 @@
         <v>937</v>
       </c>
     </row>
-    <row r="236" spans="1:10">
+    <row r="236" hidden="1" spans="1:10">
       <c r="A236" s="1">
         <v>119570</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="C236" s="1"/>
       <c r="D236" s="1" t="s">
         <v>939</v>
       </c>
@@ -11110,14 +11064,13 @@
         <v>941</v>
       </c>
     </row>
-    <row r="237" spans="1:10">
+    <row r="237" hidden="1" spans="1:10">
       <c r="A237" s="1">
         <v>119595</v>
       </c>
       <c r="B237" s="1" t="s">
         <v>942</v>
       </c>
-      <c r="C237" s="1"/>
       <c r="D237" s="1" t="s">
         <v>943</v>
       </c>
@@ -11140,7 +11093,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="238" spans="1:10">
+    <row r="238" hidden="1" spans="1:10">
       <c r="A238" s="1">
         <v>120001</v>
       </c>
@@ -11169,14 +11122,13 @@
         <v>949</v>
       </c>
     </row>
-    <row r="239" spans="1:10">
+    <row r="239" hidden="1" spans="1:10">
       <c r="A239" s="1">
         <v>119576</v>
       </c>
       <c r="B239" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="C239" s="1"/>
       <c r="D239" s="1" t="s">
         <v>951</v>
       </c>
@@ -11199,7 +11151,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="240" spans="1:10">
+    <row r="240" hidden="1" spans="1:10">
       <c r="A240" s="1">
         <v>119598</v>
       </c>
@@ -11228,7 +11180,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="241" spans="1:10">
+    <row r="241" hidden="1" spans="1:10">
       <c r="A241" s="1">
         <v>120137</v>
       </c>
@@ -11257,7 +11209,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="242" spans="1:10">
+    <row r="242" hidden="1" spans="1:10">
       <c r="A242" s="1">
         <v>121315</v>
       </c>
@@ -11286,7 +11238,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="243" spans="1:10">
+    <row r="243" hidden="1" spans="1:10">
       <c r="A243" s="1">
         <v>119554</v>
       </c>
@@ -11315,7 +11267,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="244" spans="1:10">
+    <row r="244" hidden="1" spans="1:10">
       <c r="A244" s="1">
         <v>121317</v>
       </c>
@@ -11344,7 +11296,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="245" spans="1:10">
+    <row r="245" hidden="1" spans="1:10">
       <c r="A245" s="1">
         <v>134507</v>
       </c>
@@ -11373,7 +11325,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="246" spans="1:10">
+    <row r="246" hidden="1" spans="1:10">
       <c r="A246" s="1">
         <v>119571</v>
       </c>
@@ -11402,7 +11354,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="247" spans="1:10">
+    <row r="247" hidden="1" spans="1:10">
       <c r="A247" s="1">
         <v>121275</v>
       </c>
@@ -11431,7 +11383,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="248" spans="1:10">
+    <row r="248" hidden="1" spans="1:10">
       <c r="A248" s="1">
         <v>121084</v>
       </c>
@@ -11460,7 +11412,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="249" spans="1:10">
+    <row r="249" hidden="1" spans="1:10">
       <c r="A249" s="1">
         <v>119528</v>
       </c>
@@ -11489,7 +11441,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="250" spans="1:10">
+    <row r="250" hidden="1" spans="1:10">
       <c r="A250" s="1">
         <v>121312</v>
       </c>
@@ -11518,7 +11470,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="251" spans="1:10">
+    <row r="251" hidden="1" spans="1:10">
       <c r="A251" s="1">
         <v>119579</v>
       </c>
@@ -11547,7 +11499,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="252" spans="1:10">
+    <row r="252" hidden="1" spans="1:10">
       <c r="A252" s="1">
         <v>121348</v>
       </c>
@@ -11576,14 +11528,13 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="253" spans="1:10">
+    <row r="253" hidden="1" spans="1:10">
       <c r="A253" s="1">
         <v>119476</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>1005</v>
       </c>
-      <c r="C253" s="1"/>
       <c r="D253" s="1" t="s">
         <v>1006</v>
       </c>
@@ -11606,14 +11557,13 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="254" spans="1:10">
+    <row r="254" hidden="1" spans="1:10">
       <c r="A254" s="1">
         <v>119582</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="C254" s="1"/>
       <c r="D254" s="1" t="s">
         <v>1009</v>
       </c>
@@ -11636,7 +11586,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="255" spans="1:10">
+    <row r="255" hidden="1" spans="1:10">
       <c r="A255" s="1">
         <v>120816</v>
       </c>
@@ -11665,14 +11615,13 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="256" spans="1:10">
+    <row r="256" hidden="1" spans="1:10">
       <c r="A256" s="1">
         <v>119523</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="C256" s="1"/>
       <c r="D256" s="1" t="s">
         <v>1017</v>
       </c>
@@ -11695,7 +11644,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="257" spans="1:10">
+    <row r="257" hidden="1" spans="1:10">
       <c r="A257" s="1">
         <v>165340</v>
       </c>
@@ -11724,7 +11673,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="258" spans="1:10">
+    <row r="258" hidden="1" spans="1:10">
       <c r="A258" s="1">
         <v>137248</v>
       </c>
@@ -11753,7 +11702,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="259" spans="1:10">
+    <row r="259" hidden="1" spans="1:10">
       <c r="A259" s="1">
         <v>121094</v>
       </c>
@@ -11782,7 +11731,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="260" spans="1:10">
+    <row r="260" hidden="1" spans="1:10">
       <c r="A260" s="1">
         <v>149749</v>
       </c>
@@ -11811,14 +11760,13 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="261" spans="1:10">
+    <row r="261" hidden="1" spans="1:10">
       <c r="A261" s="1">
         <v>119536</v>
       </c>
       <c r="B261" s="1" t="s">
         <v>1035</v>
       </c>
-      <c r="C261" s="1"/>
       <c r="D261" s="1" t="s">
         <v>1036</v>
       </c>
@@ -11841,7 +11789,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="262" spans="1:10">
+    <row r="262" hidden="1" spans="1:10">
       <c r="A262" s="1">
         <v>164293</v>
       </c>
@@ -11870,7 +11818,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="263" spans="1:10">
+    <row r="263" hidden="1" spans="1:10">
       <c r="A263" s="1">
         <v>345268</v>
       </c>
@@ -11899,7 +11847,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="264" spans="1:10">
+    <row r="264" hidden="1" spans="1:10">
       <c r="A264" s="1">
         <v>120988</v>
       </c>
@@ -11928,7 +11876,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="265" spans="1:10">
+    <row r="265" hidden="1" spans="1:10">
       <c r="A265" s="1">
         <v>335507</v>
       </c>
@@ -11957,7 +11905,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="266" spans="1:10">
+    <row r="266" hidden="1" spans="1:10">
       <c r="A266" s="1">
         <v>333819</v>
       </c>
@@ -11986,7 +11934,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="267" spans="1:10">
+    <row r="267" hidden="1" spans="1:10">
       <c r="A267" s="1">
         <v>309427</v>
       </c>
@@ -12015,7 +11963,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="268" spans="1:10">
+    <row r="268" hidden="1" spans="1:10">
       <c r="A268" s="1">
         <v>131733</v>
       </c>
@@ -12044,7 +11992,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="269" spans="1:10">
+    <row r="269" hidden="1" spans="1:10">
       <c r="A269" s="1">
         <v>318099</v>
       </c>
@@ -12075,7 +12023,12 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J269" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:J269">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="昌邑市中医院"/>
+      </filters>
+    </filterColumn>
+    <sortState ref="A1:J269">
       <sortCondition ref="D2"/>
     </sortState>
     <extLst/>
